--- a/10-projects/14-hyundaimokdong-marketing/현대목동점_위탁판매_대리점_계약정서_2026.xlsx
+++ b/10-projects/14-hyundaimokdong-marketing/현대목동점_위탁판매_대리점_계약정서_2026.xlsx
@@ -9509,7 +9509,7 @@
   <pageMargins left="0.59" right="0.59" top="0.71" bottom="0.71" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="313" min="0" max="10" man="1"/>
+    <brk id="309" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -22104,7 +22104,7 @@
   <pageMargins left="0.59" right="0.59" top="0.71" bottom="0.71" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="82" min="0" max="12" man="1"/>
+    <brk id="109" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -25193,10 +25193,9 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59" right="0.59" top="0.71" bottom="0.71" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="59" min="0" max="9" man="1"/>
-    <brk id="118" min="0" max="9" man="1"/>
-    <brk id="170" min="0" max="9" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="59" min="0" max="16383" man="1"/>
+    <brk id="143" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -28203,9 +28202,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59" right="0.59" top="0.71" bottom="0.71" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="64" min="0" max="10" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
 
